--- a/data/trans_dic/P1429-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1429-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,07</t>
+          <t>1,28; 3,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,22; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,33</t>
+          <t>1,29; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,29</t>
+          <t>6,38; 9,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 9,74</t>
+          <t>6,69; 9,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,76</t>
+          <t>5,1; 8,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,25</t>
+          <t>9,9; 13,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,26</t>
+          <t>4,36; 6,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,86</t>
+          <t>3,99; 5,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,14</t>
+          <t>3,22; 5,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,83</t>
+          <t>6,67; 8,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,07</t>
+          <t>0,25; 1,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,42</t>
+          <t>0,05; 0,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,52</t>
+          <t>0,08; 0,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,34</t>
+          <t>0,34; 1,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,19</t>
+          <t>1,66; 3,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,05</t>
+          <t>0,89; 2,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,02</t>
+          <t>1,61; 3,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,19</t>
+          <t>2,3; 3,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,92</t>
+          <t>1,08; 1,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,07</t>
+          <t>0,5; 1,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,6</t>
+          <t>0,86; 1,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,99</t>
+          <t>1,43; 2,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,75</t>
+          <t>0,15; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,01</t>
+          <t>0,12; 0,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,73</t>
+          <t>0,58; 2,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,75</t>
+          <t>0,84; 3,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,38</t>
+          <t>0,92; 3,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,52</t>
+          <t>1,94; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,5; 1,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,93</t>
+          <t>0,4; 1,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,12</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,01</t>
+          <t>1,07; 2,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,47</t>
+          <t>0,74; 1,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,47</t>
+          <t>0,06; 0,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,34</t>
+          <t>0,56; 1,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,0</t>
+          <t>3,6; 5,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,78</t>
+          <t>3,35; 4,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,08</t>
+          <t>2,91; 4,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,02</t>
+          <t>4,17; 5,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,12</t>
+          <t>2,33; 3,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,52</t>
+          <t>1,83; 2,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,31</t>
+          <t>1,62; 2,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,02</t>
+          <t>2,54; 3,17</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86153</t>
+          <t>94524</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97573</t>
+          <t>106557</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13773; 31663</t>
+          <t>13157; 31785</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 12110</t>
+          <t>0; 13117</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1695; 10545</t>
+          <t>1643; 10790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6931; 16998</t>
+          <t>7406; 19355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81843; 122214</t>
+          <t>83842; 123176</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91565; 130198</t>
+          <t>89370; 130863</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53025; 87091</t>
+          <t>50749; 84474</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73700; 99230</t>
+          <t>80843; 108239</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102801; 146928</t>
+          <t>102379; 145059</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93070; 135491</t>
+          <t>92236; 135237</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56151; 89966</t>
+          <t>56373; 92308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84581; 111128</t>
+          <t>92774; 122479</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70409</t>
+          <t>76161</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4916; 18095</t>
+          <t>4249; 18721</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>983; 8185</t>
+          <t>984; 9062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1829; 10858</t>
+          <t>1666; 11210</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7251; 30574</t>
+          <t>7568; 27772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26521; 50687</t>
+          <t>26363; 51334</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15706; 35898</t>
+          <t>15628; 36956</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32426; 60022</t>
+          <t>31952; 59670</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38291; 71079</t>
+          <t>49825; 75471</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35171; 63087</t>
+          <t>35385; 63913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18748; 39763</t>
+          <t>18551; 40603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35986; 64904</t>
+          <t>35117; 65428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53989; 89961</t>
+          <t>62633; 96380</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>22198</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>833; 9650</t>
+          <t>835; 9091</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,52 +1930,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7342</t>
+          <t>0; 7197</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>735; 6533</t>
+          <t>859; 6464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2840; 13024</t>
+          <t>2775; 12513</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3665; 17185</t>
+          <t>3837; 17400</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5194; 18560</t>
+          <t>5027; 19124</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11484; 23208</t>
+          <t>14198; 27468</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5218; 18194</t>
+          <t>5143; 16906</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3719; 18119</t>
+          <t>3788; 17887</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6500; 23182</t>
+          <t>6274; 21747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13347; 26186</t>
+          <t>15426; 30430</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>159113</t>
+          <t>175410</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>187430</t>
+          <t>204917</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24797; 48276</t>
+          <t>24124; 46684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2057; 16052</t>
+          <t>2085; 16256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5914; 19918</t>
+          <t>6128; 19958</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19125; 46243</t>
+          <t>19568; 44761</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121146; 169092</t>
+          <t>121541; 169876</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>119193; 169762</t>
+          <t>118998; 167194</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100033; 144158</t>
+          <t>102632; 146070</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130966; 182774</t>
+          <t>154720; 195350</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>153714; 207773</t>
+          <t>155055; 206130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126669; 175391</t>
+          <t>127505; 179078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110567; 159455</t>
+          <t>111611; 158800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>159239; 214130</t>
+          <t>183281; 229287</t>
         </is>
       </c>
     </row>
